--- a/artfynd/A 7905-2026 artfynd.xlsx
+++ b/artfynd/A 7905-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115454417</v>
+        <v>121969797</v>
       </c>
       <c r="B2" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -753,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115454418</v>
+        <v>115454417</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +791,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,11 +815,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -922,12 +898,7 @@
         <v>115454419</v>
       </c>
       <c r="B4" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,47 +1010,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121969797</v>
+        <v>115454418</v>
       </c>
       <c r="B5" t="n">
-        <v>56584</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1117,12 +1087,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7905-2026 artfynd.xlsx
+++ b/artfynd/A 7905-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121969797</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115454417</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115454419</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,8 +1146,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115454418</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>